--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/FLORIDA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/FLORIDA_2014.xlsx
@@ -643,7 +643,7 @@
         <v>24</v>
       </c>
       <c r="D16">
-        <v>0.000928792569659</v>
+        <v>0.0009287925696590002</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>24</v>
       </c>
       <c r="D70">
-        <v>0.000928792569659</v>
+        <v>0.0009287925696590002</v>
       </c>
     </row>
     <row r="71">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C151">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C157">
@@ -3361,7 +3361,7 @@
         <v>24</v>
       </c>
       <c r="D167">
-        <v>0.000928792569659</v>
+        <v>0.0009287925696590002</v>
       </c>
     </row>
     <row r="168">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C206">
@@ -4909,7 +4909,7 @@
         <v>24</v>
       </c>
       <c r="D253">
-        <v>0.000928792569659</v>
+        <v>0.0009287925696590002</v>
       </c>
     </row>
     <row r="254">
@@ -5269,7 +5269,7 @@
         <v>24</v>
       </c>
       <c r="D273">
-        <v>0.000928792569659</v>
+        <v>0.0009287925696590002</v>
       </c>
     </row>
     <row r="274">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C334">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C344">
@@ -9607,7 +9607,7 @@
         <v>24</v>
       </c>
       <c r="D514">
-        <v>0.000928792569659</v>
+        <v>0.0009287925696590002</v>
       </c>
     </row>
     <row r="515">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C777">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C917">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C918">
@@ -17952,7 +17952,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C978">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C979">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="B1410" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1410">
@@ -28860,7 +28860,7 @@
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1584">
@@ -29443,7 +29443,7 @@
         <v>24</v>
       </c>
       <c r="D1616">
-        <v>0.000928792569659</v>
+        <v>0.0009287925696590002</v>
       </c>
     </row>
     <row r="1617">
